--- a/data/source/score.xlsx
+++ b/data/source/score.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex.soo\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18956CE3-3B42-445F-93F3-2BD48D7FC0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7634AF4-D733-472E-BF46-19DC25AAB803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{74AF8C0C-EA1C-4F7A-880C-F13FC69F543F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{74AF8C0C-EA1C-4F7A-880C-F13FC69F543F}"/>
   </bookViews>
   <sheets>
     <sheet name="יב" sheetId="7" r:id="rId1"/>
@@ -552,30 +552,32 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -710,9 +712,247 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="4"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -894,169 +1134,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="4"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -1132,82 +1210,6 @@
       </fill>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1222,113 +1224,113 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{080C1092-6A0A-4762-B85A-882867EDA91E}" name="Table27" displayName="Table27" ref="A2:H64" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{080C1092-6A0A-4762-B85A-882867EDA91E}" name="Table27" displayName="Table27" ref="A2:H64" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59">
   <autoFilter ref="A2:H64" xr:uid="{080C1092-6A0A-4762-B85A-882867EDA91E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G53">
     <sortCondition descending="1" ref="A2:A53"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{9F8F0BFB-E23B-4666-AAB3-43FAF7779AC3}" name="ציון" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{0D521493-1871-44E1-843F-CD6F712EED08}" name="מתח" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{D4E1E914-08F7-45B8-8B65-15B32675FD36}" name="שכיבות סמיכה" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{1CF1B994-2351-4D57-A54B-00F09CD43FA7}" name="פלאנק" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{7BE0B3D8-7E2B-42DC-92C8-B55A312B1830}" name="3000 מטר" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{A4DE5093-75FD-41E7-BE00-22D91B07B9FF}" name="5000 מטר" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{F2389973-5075-4EFA-B610-B7581A736782}" name="ביפים" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{D0FDCBBF-3272-48CE-A9A4-F58DC5AAA84F}" name="דילגית" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{9F8F0BFB-E23B-4666-AAB3-43FAF7779AC3}" name="ציון" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{0D521493-1871-44E1-843F-CD6F712EED08}" name="מתח" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{D4E1E914-08F7-45B8-8B65-15B32675FD36}" name="שכיבות סמיכה" dataDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{1CF1B994-2351-4D57-A54B-00F09CD43FA7}" name="פלאנק" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{7BE0B3D8-7E2B-42DC-92C8-B55A312B1830}" name="3000 מטר" dataDxfId="54"/>
+    <tableColumn id="6" xr3:uid="{A4DE5093-75FD-41E7-BE00-22D91B07B9FF}" name="5000 מטר" dataDxfId="53"/>
+    <tableColumn id="7" xr3:uid="{F2389973-5075-4EFA-B610-B7581A736782}" name="ביפים" dataDxfId="52"/>
+    <tableColumn id="8" xr3:uid="{D0FDCBBF-3272-48CE-A9A4-F58DC5AAA84F}" name="דילגית" dataDxfId="51"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{94147E23-A85E-4A21-9A2E-27DC4516B37B}" name="Table16" displayName="Table16" ref="A2:H64" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{94147E23-A85E-4A21-9A2E-27DC4516B37B}" name="Table16" displayName="Table16" ref="A2:H64" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
   <autoFilter ref="A2:H64" xr:uid="{94147E23-A85E-4A21-9A2E-27DC4516B37B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G53">
     <sortCondition descending="1" ref="A2:A53"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{492854FD-E35B-48D1-A87E-A92B52CBF214}" name="ציון" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{DDDBCA0D-2822-4C22-9ED2-87FE82EBD513}" name="מתח" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{88448278-365C-4D30-BBCA-5207B2404C97}" name="שכיבות סמיכה" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{65B9B706-442D-483E-B311-AC9DD4512968}" name="פלאנק" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{32D72CA2-DCDE-45DF-A41F-403040EAA84E}" name="3000 מטר" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{50682207-9E48-48EC-901D-0E041E64826D}" name="5000 מטר" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{AB16DDF8-6439-48F6-941B-C76E98634B9A}" name="ביפים" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{692970A5-2176-42D4-8FB5-6E0BA9139E70}" name="דילגית" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{492854FD-E35B-48D1-A87E-A92B52CBF214}" name="ציון" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{DDDBCA0D-2822-4C22-9ED2-87FE82EBD513}" name="מתח" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{88448278-365C-4D30-BBCA-5207B2404C97}" name="שכיבות סמיכה" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{65B9B706-442D-483E-B311-AC9DD4512968}" name="פלאנק" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{32D72CA2-DCDE-45DF-A41F-403040EAA84E}" name="3000 מטר" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{50682207-9E48-48EC-901D-0E041E64826D}" name="5000 מטר" dataDxfId="43"/>
+    <tableColumn id="7" xr3:uid="{AB16DDF8-6439-48F6-941B-C76E98634B9A}" name="ביפים" dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{692970A5-2176-42D4-8FB5-6E0BA9139E70}" name="דילגית" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{29E20603-A604-4099-AFF8-99511F0643FC}" name="Table4" displayName="Table4" ref="A2:G64" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32" headerRowBorderDxfId="68" tableBorderDxfId="67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{29E20603-A604-4099-AFF8-99511F0643FC}" name="Table4" displayName="Table4" ref="A2:G64" totalsRowShown="0" headerRowDxfId="40" dataDxfId="38" headerRowBorderDxfId="39" tableBorderDxfId="37">
   <autoFilter ref="A2:G64" xr:uid="{29E20603-A604-4099-AFF8-99511F0643FC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E49">
     <sortCondition descending="1" ref="A2:A49"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{FE6CC9CC-B359-4CBB-9B22-E514F748ABF2}" name="ציון" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{64329BC6-CE57-4FFE-9980-CAA0E7A7D26E}" name="דילגית" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{90F7412E-D96E-477C-8089-0079B2067C49}" name="ביפים" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{39F4868C-2E7B-4E5F-8B90-9F77DDA2E634}" name="שכיבות סמיכה" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{6BD50668-6CCF-413F-A32C-E5760DBE6D74}" name="פלאנק " dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{E3097417-FDBB-450D-94E5-E4034770FB6B}" name="מתח" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{62D46C0E-6C1F-4F30-9A87-6DF2F124FCB5}" name="1800 מטר" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{FE6CC9CC-B359-4CBB-9B22-E514F748ABF2}" name="ציון" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{64329BC6-CE57-4FFE-9980-CAA0E7A7D26E}" name="דילגית" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{90F7412E-D96E-477C-8089-0079B2067C49}" name="ביפים" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{39F4868C-2E7B-4E5F-8B90-9F77DDA2E634}" name="שכיבות סמיכה" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{6BD50668-6CCF-413F-A32C-E5760DBE6D74}" name="פלאנק " dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{E3097417-FDBB-450D-94E5-E4034770FB6B}" name="מתח" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{62D46C0E-6C1F-4F30-9A87-6DF2F124FCB5}" name="1800 מטר" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E1E70D8B-B0AA-46FD-8BC5-813B9BB79CF9}" name="Table3" displayName="Table3" ref="A2:F64" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41" headerRowBorderDxfId="66" tableBorderDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E1E70D8B-B0AA-46FD-8BC5-813B9BB79CF9}" name="Table3" displayName="Table3" ref="A2:F64" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26">
   <autoFilter ref="A2:F64" xr:uid="{E1E70D8B-B0AA-46FD-8BC5-813B9BB79CF9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E49">
     <sortCondition descending="1" ref="A2:A49"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{64BC6406-6D53-457A-AC99-6D5DEFCB0FCE}" name="ציון" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{9697C709-CF46-4E48-9CA9-E503FBE83D6A}" name="דילגית" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{1F06DB66-2F59-44F2-95C1-02AED8A02F1A}" name="ביפים" dataDxfId="46"/>
-    <tableColumn id="4" xr3:uid="{7115BFE4-9191-42F7-B8A8-013C9C91DB00}" name="שכיבות סמיכה" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{2CDE18B5-5ACC-4846-8F26-A97F28FC6C1F}" name="פלאנק " dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{878CEDE2-0F6D-4F96-ACFF-E203EB8A0A51}" name="1800 מטר" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{64BC6406-6D53-457A-AC99-6D5DEFCB0FCE}" name="ציון" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{9697C709-CF46-4E48-9CA9-E503FBE83D6A}" name="דילגית" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{1F06DB66-2F59-44F2-95C1-02AED8A02F1A}" name="ביפים" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{7115BFE4-9191-42F7-B8A8-013C9C91DB00}" name="שכיבות סמיכה" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{2CDE18B5-5ACC-4846-8F26-A97F28FC6C1F}" name="פלאנק " dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{878CEDE2-0F6D-4F96-ACFF-E203EB8A0A51}" name="1800 מטר" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{09D14F04-76A3-452C-8575-F0538389E116}" name="Table2" displayName="Table2" ref="A2:F64" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{09D14F04-76A3-452C-8575-F0538389E116}" name="Table2" displayName="Table2" ref="A2:F64" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="A2:F64" xr:uid="{09D14F04-76A3-452C-8575-F0538389E116}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E49">
     <sortCondition descending="1" ref="A2:A49"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{EC973BC6-7767-4327-AB02-5D284DD91B28}" name="ציון" dataDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{2F052BC8-A3D9-4209-9216-0DE462B77740}" name="דילגית" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{85B845DF-86FE-453E-9D60-02FC98598D05}" name="ביפים" dataDxfId="54"/>
-    <tableColumn id="4" xr3:uid="{F3E5C8CB-FE6F-4CB7-B7A3-26376D3A5E49}" name="שכיבות סמיכה" dataDxfId="53"/>
-    <tableColumn id="5" xr3:uid="{5CF3D8C9-A350-4215-9EE8-BF5E6961600E}" name="פלאנק " dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{DF69E92E-E4DA-4026-B573-E98BCE1BC821}" name="1300 מטר" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{EC973BC6-7767-4327-AB02-5D284DD91B28}" name="ציון" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{2F052BC8-A3D9-4209-9216-0DE462B77740}" name="דילגית" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{85B845DF-86FE-453E-9D60-02FC98598D05}" name="ביפים" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{F3E5C8CB-FE6F-4CB7-B7A3-26376D3A5E49}" name="שכיבות סמיכה" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{5CF3D8C9-A350-4215-9EE8-BF5E6961600E}" name="פלאנק " dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{DF69E92E-E4DA-4026-B573-E98BCE1BC821}" name="1300 מטר" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2ED811A0-34D1-43D3-A5AA-93FBB51D0F9A}" name="Table1" displayName="Table1" ref="A2:F64" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2ED811A0-34D1-43D3-A5AA-93FBB51D0F9A}" name="Table1" displayName="Table1" ref="A2:F64" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67">
   <autoFilter ref="A2:F64" xr:uid="{2ED811A0-34D1-43D3-A5AA-93FBB51D0F9A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E49">
     <sortCondition descending="1" ref="A2:A49"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7E4721B2-8516-4CB0-86CC-7572FBA9596A}" name="ציון" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{594E3E7D-091A-41DC-B0CC-75B59A8C6A3A}" name="דילגית" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{7461DB03-2A6B-4292-A9E0-8F5A4087F8B2}" name="ביפים" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{460F8069-EFF0-4BA1-8E4E-8DE54F6FB287}" name="שכיבות סמיכה" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{60D881A4-6122-4C2E-BF49-9E3D4738B085}" name="פלאנק " dataDxfId="60"/>
-    <tableColumn id="6" xr3:uid="{1777AEB9-26E6-43B6-8B88-CDD701F729CA}" name="1300 מטר" dataDxfId="59"/>
+    <tableColumn id="1" xr3:uid="{7E4721B2-8516-4CB0-86CC-7572FBA9596A}" name="ציון" dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{594E3E7D-091A-41DC-B0CC-75B59A8C6A3A}" name="דילגית" dataDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{7461DB03-2A6B-4292-A9E0-8F5A4087F8B2}" name="ביפים" dataDxfId="64"/>
+    <tableColumn id="4" xr3:uid="{460F8069-EFF0-4BA1-8E4E-8DE54F6FB287}" name="שכיבות סמיכה" dataDxfId="63"/>
+    <tableColumn id="5" xr3:uid="{60D881A4-6122-4C2E-BF49-9E3D4738B085}" name="פלאנק " dataDxfId="62"/>
+    <tableColumn id="6" xr3:uid="{1777AEB9-26E6-43B6-8B88-CDD701F729CA}" name="1300 מטר" dataDxfId="61"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1654,38 +1656,37 @@
   <dimension ref="A2:M64"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7265625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.54296875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.08984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7265625" style="6"/>
-    <col min="10" max="13" width="8.7265625" style="5"/>
-    <col min="14" max="16384" width="8.7265625" style="6"/>
+    <col min="1" max="1" width="5.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.36328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.54296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" style="5"/>
+    <col min="14" max="16384" width="8.7265625" style="5"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -1702,7 +1703,7 @@
       <c r="C3" s="1">
         <v>50</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>2.0833333333333333E-3</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -1726,7 +1727,7 @@
       <c r="C4" s="1">
         <v>49</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <v>2.0370370370370369E-3</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -1752,7 +1753,7 @@
       <c r="C5" s="1">
         <v>48</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>1.99074074074074E-3</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -1778,7 +1779,7 @@
       <c r="C6" s="1">
         <v>47</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>1.9444444444444401E-3</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -1802,7 +1803,7 @@
       <c r="C7" s="1">
         <v>46</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>1.8981481481481501E-3</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -1828,7 +1829,7 @@
       <c r="C8" s="1">
         <v>45</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>1.85185185185185E-3</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -1854,7 +1855,7 @@
       <c r="C9" s="1">
         <v>44</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>4.3495370370370372E-2</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -1878,7 +1879,7 @@
       <c r="C10" s="1">
         <v>43</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>8.5138888888888903E-2</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -1904,7 +1905,7 @@
       <c r="C11" s="1">
         <v>42</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>0.12678240740740801</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -1924,13 +1925,11 @@
       <c r="A12" s="1">
         <v>91</v>
       </c>
-      <c r="B12" s="1">
-        <v>14</v>
-      </c>
+      <c r="B12" s="10"/>
       <c r="C12" s="1">
         <v>41</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>0.16842592592592601</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -1950,11 +1949,13 @@
       <c r="A13" s="1">
         <v>90</v>
       </c>
-      <c r="B13" s="1"/>
+      <c r="B13" s="1">
+        <v>14</v>
+      </c>
       <c r="C13" s="1">
         <v>40</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>0.210069444444445</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -1980,7 +1981,7 @@
       <c r="C14" s="1">
         <v>39</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>0.25171296296296303</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -1995,7 +1996,7 @@
       <c r="H14" s="1">
         <v>148</v>
       </c>
-      <c r="I14" s="5"/>
+      <c r="I14"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
@@ -2007,7 +2008,7 @@
       <c r="C15" s="1">
         <v>38</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <v>0.29335648148148202</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -2022,7 +2023,7 @@
       <c r="H15" s="1">
         <v>146</v>
       </c>
-      <c r="I15" s="5"/>
+      <c r="I15"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
@@ -2032,7 +2033,7 @@
       <c r="C16" s="1">
         <v>37</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <v>0.33500000000000002</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -2047,7 +2048,7 @@
       <c r="H16" s="1">
         <v>144</v>
       </c>
-      <c r="I16" s="5"/>
+      <c r="I16"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
@@ -2059,7 +2060,7 @@
       <c r="C17" s="1">
         <v>36</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>0.37664351851851902</v>
       </c>
       <c r="E17" s="3" t="s">
@@ -2074,7 +2075,7 @@
       <c r="H17" s="1">
         <v>142</v>
       </c>
-      <c r="I17" s="5"/>
+      <c r="I17"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
@@ -2086,7 +2087,7 @@
       <c r="C18" s="1">
         <v>35</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <v>0.41828703703703701</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -2101,7 +2102,7 @@
       <c r="H18" s="1">
         <v>140</v>
       </c>
-      <c r="I18" s="5"/>
+      <c r="I18"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
@@ -2111,7 +2112,7 @@
       <c r="C19" s="1">
         <v>34</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>0.45993055555555601</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -2126,7 +2127,7 @@
       <c r="H19" s="1">
         <v>138</v>
       </c>
-      <c r="I19" s="5"/>
+      <c r="I19"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
@@ -2138,7 +2139,7 @@
       <c r="C20" s="1">
         <v>33</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>0.50157407407407395</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -2153,7 +2154,7 @@
       <c r="H20" s="1">
         <v>136</v>
       </c>
-      <c r="I20" s="5"/>
+      <c r="I20"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
@@ -2165,7 +2166,7 @@
       <c r="C21" s="1">
         <v>32</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>0.54321759259259295</v>
       </c>
       <c r="E21" s="3" t="s">
@@ -2180,7 +2181,7 @@
       <c r="H21" s="1">
         <v>134</v>
       </c>
-      <c r="I21" s="5"/>
+      <c r="I21"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
@@ -2190,7 +2191,7 @@
       <c r="C22" s="1">
         <v>31</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <v>0.58486111111111105</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -2216,7 +2217,7 @@
       <c r="C23" s="1">
         <v>30</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="9">
         <v>0.62650462962963005</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -2240,7 +2241,7 @@
       <c r="C24" s="1">
         <v>29</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="9">
         <v>0.66814814814814805</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -2266,7 +2267,7 @@
       <c r="C25" s="1">
         <v>28</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="9">
         <v>0.70979166666666704</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -2290,7 +2291,7 @@
       <c r="C26" s="1">
         <v>27</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="9">
         <v>0.75143518518518504</v>
       </c>
       <c r="E26" s="3" t="s">
@@ -2314,7 +2315,7 @@
       <c r="C27" s="1">
         <v>26</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="9">
         <v>0.79307870370370404</v>
       </c>
       <c r="E27" s="3" t="s">
@@ -2340,7 +2341,7 @@
       <c r="C28" s="1">
         <v>25</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="9">
         <v>0.83472222222222203</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -2364,7 +2365,7 @@
       <c r="C29" s="1">
         <v>24</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="9">
         <v>0.87636574074074103</v>
       </c>
       <c r="E29" s="3" t="s">
@@ -2388,7 +2389,7 @@
       <c r="C30" s="1">
         <v>23</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="9">
         <v>0.91800925925925903</v>
       </c>
       <c r="E30" s="3" t="s">
@@ -2412,7 +2413,7 @@
       <c r="C31" s="1">
         <v>22</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <v>0.95965277777777802</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -2436,7 +2437,7 @@
       <c r="C32" s="1">
         <v>21</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="9">
         <v>1.0012962962962999</v>
       </c>
       <c r="E32" s="3" t="s">
@@ -2462,7 +2463,7 @@
       <c r="C33" s="1">
         <v>20</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="9">
         <v>1.0429398148148099</v>
       </c>
       <c r="E33" s="3" t="s">
@@ -2486,7 +2487,7 @@
       <c r="C34" s="1">
         <v>19</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="9">
         <v>1.0845833333333299</v>
       </c>
       <c r="E34" s="3" t="s">
@@ -2510,7 +2511,7 @@
       <c r="C35" s="1">
         <v>18</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="9">
         <v>1.1262268518518499</v>
       </c>
       <c r="E35" s="3" t="s">
@@ -2534,7 +2535,7 @@
       <c r="C36" s="1">
         <v>17</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="9">
         <v>1.1678703703703699</v>
       </c>
       <c r="E36" s="3" t="s">
@@ -2558,7 +2559,7 @@
       <c r="C37" s="1">
         <v>16</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D37" s="9">
         <v>1.2095138888888901</v>
       </c>
       <c r="E37" s="3" t="s">
@@ -2582,7 +2583,7 @@
       <c r="C38" s="1">
         <v>15</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="9">
         <v>1.2511574074074101</v>
       </c>
       <c r="E38" s="3" t="s">
@@ -2606,7 +2607,7 @@
       <c r="C39" s="1">
         <v>14</v>
       </c>
-      <c r="D39" s="10">
+      <c r="D39" s="9">
         <v>1.2928009259259201</v>
       </c>
       <c r="E39" s="3" t="s">
@@ -2630,7 +2631,7 @@
       <c r="C40" s="1">
         <v>13</v>
       </c>
-      <c r="D40" s="10">
+      <c r="D40" s="9">
         <v>1.3344444444444401</v>
       </c>
       <c r="E40" s="3" t="s">
@@ -2654,7 +2655,7 @@
       <c r="C41" s="1">
         <v>12</v>
       </c>
-      <c r="D41" s="10">
+      <c r="D41" s="9">
         <v>1.3760879629629601</v>
       </c>
       <c r="E41" s="3" t="s">
@@ -2678,7 +2679,7 @@
       <c r="C42" s="1">
         <v>11</v>
       </c>
-      <c r="D42" s="10">
+      <c r="D42" s="9">
         <v>1.4177314814814801</v>
       </c>
       <c r="E42" s="3" t="s">
@@ -2704,7 +2705,7 @@
       <c r="C43" s="1">
         <v>10</v>
       </c>
-      <c r="D43" s="10">
+      <c r="D43" s="9">
         <v>1.4593750000000001</v>
       </c>
       <c r="E43" s="3" t="s">
@@ -2728,7 +2729,7 @@
       <c r="C44" s="1">
         <v>9</v>
       </c>
-      <c r="D44" s="10">
+      <c r="D44" s="9">
         <v>1.5010185185185201</v>
       </c>
       <c r="E44" s="3" t="s">
@@ -2750,7 +2751,7 @@
       <c r="C45" s="1">
         <v>8</v>
       </c>
-      <c r="D45" s="10">
+      <c r="D45" s="9">
         <v>1.5426620370370401</v>
       </c>
       <c r="E45" s="3" t="s">
@@ -2774,7 +2775,7 @@
       <c r="C46" s="1">
         <v>7</v>
       </c>
-      <c r="D46" s="10">
+      <c r="D46" s="9">
         <v>1.5843055555555501</v>
       </c>
       <c r="E46" s="3" t="s">
@@ -2798,7 +2799,7 @@
       <c r="C47" s="1">
         <v>6</v>
       </c>
-      <c r="D47" s="10">
+      <c r="D47" s="9">
         <v>1.6259490740740701</v>
       </c>
       <c r="E47" s="3" t="s">
@@ -2822,7 +2823,7 @@
       <c r="C48" s="1">
         <v>5</v>
       </c>
-      <c r="D48" s="10">
+      <c r="D48" s="9">
         <v>1.6675925925925901</v>
       </c>
       <c r="E48" s="3" t="s">
@@ -2846,7 +2847,7 @@
       <c r="C49" s="1">
         <v>4</v>
       </c>
-      <c r="D49" s="10">
+      <c r="D49" s="9">
         <v>1.7092361111110801</v>
       </c>
       <c r="E49" s="3" t="s">
@@ -2870,7 +2871,7 @@
       <c r="C50" s="1">
         <v>3</v>
       </c>
-      <c r="D50" s="10">
+      <c r="D50" s="9">
         <v>1.7508796296295901</v>
       </c>
       <c r="E50" s="3" t="s">
@@ -2894,7 +2895,7 @@
       <c r="C51" s="1">
         <v>2</v>
       </c>
-      <c r="D51" s="10">
+      <c r="D51" s="9">
         <v>1.7925231481481001</v>
       </c>
       <c r="E51" s="3" t="s">
@@ -2915,10 +2916,8 @@
         <v>51</v>
       </c>
       <c r="B52" s="1"/>
-      <c r="C52" s="1">
-        <v>1</v>
-      </c>
-      <c r="D52" s="10">
+      <c r="C52" s="10"/>
+      <c r="D52" s="9">
         <v>1.8341666666666101</v>
       </c>
       <c r="E52" s="3" t="s">
@@ -2939,8 +2938,10 @@
         <v>50</v>
       </c>
       <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="10">
+      <c r="C53" s="1">
+        <v>1</v>
+      </c>
+      <c r="D53" s="9">
         <v>1.8758101851851201</v>
       </c>
       <c r="E53" s="3" t="s">
@@ -2962,7 +2963,7 @@
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="10">
+      <c r="D54" s="9">
         <v>1.9174537037036301</v>
       </c>
       <c r="E54" s="3" t="s">
@@ -2984,7 +2985,7 @@
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
-      <c r="D55" s="10">
+      <c r="D55" s="9">
         <v>1.9590972222221399</v>
       </c>
       <c r="E55" s="3" t="s">
@@ -3006,7 +3007,7 @@
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
-      <c r="D56" s="10">
+      <c r="D56" s="9">
         <v>2.0007407407406501</v>
       </c>
       <c r="E56" s="3" t="s">
@@ -3028,7 +3029,7 @@
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
-      <c r="D57" s="10">
+      <c r="D57" s="9">
         <v>2.0423842592591601</v>
       </c>
       <c r="E57" s="3" t="s">
@@ -3050,7 +3051,7 @@
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
-      <c r="D58" s="10">
+      <c r="D58" s="9">
         <v>2.0840277777776701</v>
       </c>
       <c r="E58" s="3" t="s">
@@ -3072,7 +3073,7 @@
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
-      <c r="D59" s="10">
+      <c r="D59" s="9">
         <v>2.1256712962961801</v>
       </c>
       <c r="E59" s="3" t="s">
@@ -3094,7 +3095,7 @@
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
-      <c r="D60" s="10">
+      <c r="D60" s="9">
         <v>2.1673148148146901</v>
       </c>
       <c r="E60" s="3" t="s">
@@ -3116,7 +3117,7 @@
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
-      <c r="D61" s="10">
+      <c r="D61" s="9">
         <v>2.2089583333332001</v>
       </c>
       <c r="E61" s="3" t="s">
@@ -3138,7 +3139,7 @@
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
-      <c r="D62" s="10">
+      <c r="D62" s="9">
         <v>2.2506018518517101</v>
       </c>
       <c r="E62" s="3" t="s">
@@ -3160,7 +3161,7 @@
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="10">
+      <c r="D63" s="9">
         <v>2.2922453703702201</v>
       </c>
       <c r="E63" s="3" t="s">
@@ -3216,36 +3217,35 @@
   <dimension ref="A2:H64"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.08984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.7265625" style="5"/>
+    <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -3262,7 +3262,7 @@
       <c r="C3" s="1">
         <v>45</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>0.210243055555553</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -3286,7 +3286,7 @@
       <c r="C4" s="1">
         <v>44</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <v>0.210208333333332</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -3312,7 +3312,7 @@
       <c r="C5" s="1">
         <v>43</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>0.21017361111110999</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -3336,7 +3336,7 @@
       <c r="C6" s="1">
         <v>42</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>0.21013888888888799</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -3362,7 +3362,7 @@
       <c r="C7" s="1">
         <v>41</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>0.21010416666666668</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -3382,11 +3382,13 @@
       <c r="A8" s="1">
         <v>95</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1">
+        <v>15</v>
+      </c>
       <c r="C8" s="1">
         <v>40</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>0.210069444444445</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -3406,13 +3408,11 @@
       <c r="A9" s="1">
         <v>94</v>
       </c>
-      <c r="B9" s="1">
-        <v>15</v>
-      </c>
+      <c r="B9" s="10"/>
       <c r="C9" s="1">
         <v>39</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>0.21004629629629629</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -3432,11 +3432,13 @@
       <c r="A10" s="1">
         <v>93</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1">
+        <v>14</v>
+      </c>
       <c r="C10" s="1">
         <v>38</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>0.21002314814814799</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -3456,13 +3458,11 @@
       <c r="A11" s="1">
         <v>92</v>
       </c>
-      <c r="B11" s="1">
-        <v>14</v>
-      </c>
+      <c r="B11" s="10"/>
       <c r="C11" s="1">
         <v>37</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>0.20999999999999899</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -3486,7 +3486,7 @@
       <c r="C12" s="1">
         <v>36</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>0.20997685185185</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -3512,7 +3512,7 @@
       <c r="C13" s="1">
         <v>35</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>0.20995370370370101</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -3536,7 +3536,7 @@
       <c r="C14" s="1">
         <v>34</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>0.20993055555555301</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -3562,7 +3562,7 @@
       <c r="C15" s="1">
         <v>33</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <v>0.20990740740740399</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -3586,7 +3586,7 @@
       <c r="C16" s="1">
         <v>32</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <v>0.209884259259255</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -3606,13 +3606,11 @@
       <c r="A17" s="1">
         <v>86</v>
       </c>
-      <c r="B17" s="1">
-        <v>11</v>
-      </c>
+      <c r="B17" s="10"/>
       <c r="C17" s="1">
         <v>31</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>0.209861111111107</v>
       </c>
       <c r="E17" s="3" t="s">
@@ -3632,11 +3630,13 @@
       <c r="A18" s="1">
         <v>85</v>
       </c>
-      <c r="B18" s="1"/>
+      <c r="B18" s="1">
+        <v>11</v>
+      </c>
       <c r="C18" s="1">
         <v>30</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <v>0.20983796296295801</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -3662,7 +3662,7 @@
       <c r="C19" s="1">
         <v>29</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>0.20981481481480899</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -3686,7 +3686,7 @@
       <c r="C20" s="1">
         <v>28</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>0.20979166666665999</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -3712,7 +3712,7 @@
       <c r="C21" s="1">
         <v>27</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>0.209768518518512</v>
       </c>
       <c r="E21" s="3" t="s">
@@ -3736,7 +3736,7 @@
       <c r="C22" s="1">
         <v>26</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <v>0.209745370370363</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -3762,7 +3762,7 @@
       <c r="C23" s="1">
         <v>25</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="9">
         <v>0.20972222222221401</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -3786,7 +3786,7 @@
       <c r="C24" s="1">
         <v>24</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="9">
         <v>0.20969907407406599</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -3812,7 +3812,7 @@
       <c r="C25" s="1">
         <v>23</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="9">
         <v>0.20967592592591699</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -3836,7 +3836,7 @@
       <c r="C26" s="1">
         <v>22</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="9">
         <v>0.209652777777768</v>
       </c>
       <c r="E26" s="3" t="s">
@@ -3856,13 +3856,11 @@
       <c r="A27" s="1">
         <v>76</v>
       </c>
-      <c r="B27" s="1">
-        <v>6</v>
-      </c>
+      <c r="B27" s="10"/>
       <c r="C27" s="1">
         <v>21</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="9">
         <v>0.20962962962961901</v>
       </c>
       <c r="E27" s="3" t="s">
@@ -3882,11 +3880,13 @@
       <c r="A28" s="1">
         <v>75</v>
       </c>
-      <c r="B28" s="1"/>
+      <c r="B28" s="1">
+        <v>6</v>
+      </c>
       <c r="C28" s="1">
         <v>20</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="9">
         <v>0.20960648148147101</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -3912,7 +3912,7 @@
       <c r="C29" s="1">
         <v>19</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="9">
         <v>0.20958333333332199</v>
       </c>
       <c r="E29" s="3" t="s">
@@ -3936,7 +3936,7 @@
       <c r="C30" s="1">
         <v>18</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="9">
         <v>0.209560185185173</v>
       </c>
       <c r="E30" s="3" t="s">
@@ -3960,7 +3960,7 @@
       <c r="C31" s="1">
         <v>17</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <v>0.209537037037025</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -3984,7 +3984,7 @@
       <c r="C32" s="1">
         <v>16</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="9">
         <v>0.20951388888887601</v>
       </c>
       <c r="E32" s="3" t="s">
@@ -4004,11 +4004,13 @@
       <c r="A33" s="1">
         <v>70</v>
       </c>
-      <c r="B33" s="1"/>
+      <c r="B33" s="1">
+        <v>4</v>
+      </c>
       <c r="C33" s="1">
         <v>15</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="9">
         <v>0.20949074074072699</v>
       </c>
       <c r="E33" s="3" t="s">
@@ -4028,13 +4030,11 @@
       <c r="A34" s="1">
         <v>69</v>
       </c>
-      <c r="B34" s="1">
-        <v>4</v>
-      </c>
+      <c r="B34" s="10"/>
       <c r="C34" s="1">
         <v>14</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="9">
         <v>0.20946759259257799</v>
       </c>
       <c r="E34" s="3" t="s">
@@ -4058,7 +4058,7 @@
       <c r="C35" s="1">
         <v>13</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="9">
         <v>0.20944444444443</v>
       </c>
       <c r="E35" s="3" t="s">
@@ -4082,7 +4082,7 @@
       <c r="C36" s="1">
         <v>12</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="9">
         <v>0.20942129629628101</v>
       </c>
       <c r="E36" s="3" t="s">
@@ -4104,7 +4104,7 @@
       <c r="C37" s="1">
         <v>11</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D37" s="9">
         <v>0.20939814814813201</v>
       </c>
       <c r="E37" s="3" t="s">
@@ -4124,11 +4124,13 @@
       <c r="A38" s="1">
         <v>65</v>
       </c>
-      <c r="B38" s="1"/>
+      <c r="B38" s="1">
+        <v>3</v>
+      </c>
       <c r="C38" s="1">
         <v>10</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="9">
         <v>0.20937499999998399</v>
       </c>
       <c r="E38" s="3" t="s">
@@ -4148,11 +4150,9 @@
       <c r="A39" s="1">
         <v>64</v>
       </c>
-      <c r="B39" s="1">
-        <v>3</v>
-      </c>
+      <c r="B39" s="10"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="10">
+      <c r="D39" s="9">
         <v>0.209351851851835</v>
       </c>
       <c r="E39" s="3" t="s">
@@ -4176,7 +4176,7 @@
       <c r="C40" s="1">
         <v>9</v>
       </c>
-      <c r="D40" s="10">
+      <c r="D40" s="9">
         <v>0.209328703703686</v>
       </c>
       <c r="E40" s="3" t="s">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
-      <c r="D41" s="10">
+      <c r="D41" s="9">
         <v>0.20930555555553701</v>
       </c>
       <c r="E41" s="3" t="s">
@@ -4217,10 +4217,8 @@
         <v>61</v>
       </c>
       <c r="B42" s="1"/>
-      <c r="C42" s="1">
-        <v>8</v>
-      </c>
-      <c r="D42" s="10">
+      <c r="C42" s="10"/>
+      <c r="D42" s="9">
         <v>0.20928240740738899</v>
       </c>
       <c r="E42" s="3" t="s">
@@ -4243,8 +4241,10 @@
       <c r="B43" s="1">
         <v>2</v>
       </c>
-      <c r="C43" s="1"/>
-      <c r="D43" s="10">
+      <c r="C43" s="1">
+        <v>8</v>
+      </c>
+      <c r="D43" s="9">
         <v>0.20925925925923999</v>
       </c>
       <c r="E43" s="3" t="s">
@@ -4268,7 +4268,7 @@
       <c r="C44" s="1">
         <v>7</v>
       </c>
-      <c r="D44" s="10">
+      <c r="D44" s="9">
         <v>0.209236111111091</v>
       </c>
       <c r="E44" s="3" t="s">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
-      <c r="D45" s="10">
+      <c r="D45" s="9">
         <v>0.20921296296294301</v>
       </c>
       <c r="E45" s="3" t="s">
@@ -4312,7 +4312,7 @@
       <c r="C46" s="1">
         <v>6</v>
       </c>
-      <c r="D46" s="10">
+      <c r="D46" s="9">
         <v>0.20918981481479401</v>
       </c>
       <c r="E46" s="3" t="s">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
-      <c r="D47" s="10">
+      <c r="D47" s="9">
         <v>0.20916666666664499</v>
       </c>
       <c r="E47" s="3" t="s">
@@ -4356,7 +4356,7 @@
       <c r="C48" s="1">
         <v>5</v>
       </c>
-      <c r="D48" s="10">
+      <c r="D48" s="9">
         <v>0.209143518518496</v>
       </c>
       <c r="E48" s="3" t="s">
@@ -4380,7 +4380,7 @@
         <v>1</v>
       </c>
       <c r="C49" s="1"/>
-      <c r="D49" s="10">
+      <c r="D49" s="9">
         <v>0.209120370370347</v>
       </c>
       <c r="E49" s="3" t="s">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
-      <c r="D50" s="10">
+      <c r="D50" s="9">
         <v>0.20909722222219801</v>
       </c>
       <c r="E50" s="3" t="s">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
-      <c r="D51" s="10">
+      <c r="D51" s="9">
         <v>0.20907407407404899</v>
       </c>
       <c r="E51" s="3" t="s">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
-      <c r="D52" s="10">
+      <c r="D52" s="9">
         <v>0.20905092592589999</v>
       </c>
       <c r="E52" s="3" t="s">
@@ -4464,7 +4464,7 @@
       <c r="C53" s="1">
         <v>4</v>
       </c>
-      <c r="D53" s="10">
+      <c r="D53" s="9">
         <v>0.209027777777751</v>
       </c>
       <c r="E53" s="3" t="s">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="10">
+      <c r="D54" s="9">
         <v>0.20900462962960201</v>
       </c>
       <c r="E54" s="3" t="s">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
-      <c r="D55" s="10">
+      <c r="D55" s="9">
         <v>0.20898148148145301</v>
       </c>
       <c r="E55" s="3" t="s">
@@ -4532,7 +4532,7 @@
       <c r="C56" s="1">
         <v>3</v>
       </c>
-      <c r="D56" s="10">
+      <c r="D56" s="9">
         <v>0.20895833333330399</v>
       </c>
       <c r="E56" s="3" t="s">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
-      <c r="D57" s="10">
+      <c r="D57" s="9">
         <v>0.208935185185155</v>
       </c>
       <c r="E57" s="3" t="s">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
-      <c r="D58" s="10">
+      <c r="D58" s="9">
         <v>0.208912037037006</v>
       </c>
       <c r="E58" s="3" t="s">
@@ -4600,7 +4600,7 @@
       <c r="C59" s="1">
         <v>2</v>
       </c>
-      <c r="D59" s="10">
+      <c r="D59" s="9">
         <v>0.20888888888885701</v>
       </c>
       <c r="E59" s="3" t="s">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
-      <c r="D60" s="10">
+      <c r="D60" s="9">
         <v>0.20886574074070799</v>
       </c>
       <c r="E60" s="3" t="s">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
-      <c r="D61" s="10">
+      <c r="D61" s="9">
         <v>0.208842592592559</v>
       </c>
       <c r="E61" s="3" t="s">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
-      <c r="D62" s="10">
+      <c r="D62" s="9">
         <v>0.20881944444441</v>
       </c>
       <c r="E62" s="3" t="s">
@@ -4688,7 +4688,7 @@
       <c r="C63" s="1">
         <v>1</v>
       </c>
-      <c r="D63" s="10">
+      <c r="D63" s="9">
         <v>0.20879629629626101</v>
       </c>
       <c r="E63" s="3" t="s">
@@ -4743,18 +4743,17 @@
   <dimension ref="A2:G64"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.26953125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.08984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.7265625" style="5"/>
+    <col min="1" max="1" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -4766,7 +4765,7 @@
       <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -4777,1227 +4776,1227 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
+      <c r="A3">
         <v>100</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3">
         <v>150</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3">
         <v>122</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3">
         <v>45</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3">
         <v>235</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3">
         <v>13</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3">
         <v>800</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
+      <c r="A4">
         <v>99</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>148</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4">
         <v>1110</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4">
         <v>44</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4">
         <v>232</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4">
         <v>803</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
+      <c r="A5">
         <v>98</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>146</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5">
         <v>117</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5">
         <v>43</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5">
         <v>229</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5">
         <v>806</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
+      <c r="A6">
         <v>97</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>144</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6">
         <v>113</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6">
         <v>42</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6">
         <v>226</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6">
         <v>809</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
+      <c r="A7">
         <v>96</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>142</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7">
         <v>11</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7">
         <v>41</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7">
         <v>223</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7">
         <v>812</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
+      <c r="A8">
         <v>95</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>140</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8">
         <v>108</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8">
         <v>40</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8">
         <v>220</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8">
         <v>12</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8">
         <v>815</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
+      <c r="A9">
         <v>94</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9">
         <v>138</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9">
         <v>105</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9">
         <v>218</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9">
         <v>818</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="5">
+      <c r="A10">
         <v>93</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10">
         <v>136</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10">
         <v>102</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10">
         <v>39</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10">
         <v>216</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10">
         <v>821</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="5">
+      <c r="A11">
         <v>92</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11">
         <v>134</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11">
         <v>99</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11">
         <v>38</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11">
         <v>214</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11">
         <v>824</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="5">
+      <c r="A12">
         <v>91</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12">
         <v>132</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12">
         <v>96</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12">
         <v>37</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12">
         <v>212</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12">
         <v>827</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="5">
+      <c r="A13">
         <v>90</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13">
         <v>130</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13">
         <v>93</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13">
         <v>36</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13">
         <v>210</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13">
         <v>11</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13">
         <v>830</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="5">
+      <c r="A14">
         <v>89</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14">
         <v>128</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14">
         <v>91</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14">
         <v>208</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14">
         <v>833</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="5">
+      <c r="A15">
         <v>88</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15">
         <v>126</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15">
         <v>90</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15">
         <v>35</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15">
         <v>206</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15">
         <v>836</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="5">
+      <c r="A16">
         <v>87</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16">
         <v>124</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16">
         <v>89</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16">
         <v>34</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16">
         <v>204</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16">
         <v>839</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="5">
+      <c r="A17">
         <v>86</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17">
         <v>122</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17">
         <v>88</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17">
         <v>33</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17">
         <v>202</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17">
         <v>842</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="5">
+      <c r="A18">
         <v>85</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18">
         <v>120</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18">
         <v>86</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18">
         <v>32</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18">
         <v>200</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18">
         <v>10</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18">
         <v>845</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="5">
+      <c r="A19">
         <v>84</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19">
         <v>118</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19">
         <v>84</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19">
         <v>158</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19">
         <v>848</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="5">
+      <c r="A20">
         <v>83</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20">
         <v>116</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20">
         <v>83</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20">
         <v>31</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20">
         <v>156</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20">
         <v>851</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="5">
+      <c r="A21">
         <v>82</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21">
         <v>114</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21">
         <v>82</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21">
         <v>30</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21">
         <v>154</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21">
         <v>854</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="5">
+      <c r="A22">
         <v>81</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22">
         <v>112</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22">
         <v>81</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22">
         <v>29</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22">
         <v>152</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22">
         <v>857</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="5">
+      <c r="A23">
         <v>80</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23">
         <v>110</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23">
         <v>79</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23">
         <v>28</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23">
         <v>150</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23">
         <v>9</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23">
         <v>900</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="5">
+      <c r="A24">
         <v>79</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24">
         <v>108</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24">
         <v>78</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24">
         <v>148</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24">
         <v>903</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="5">
+      <c r="A25">
         <v>78</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25">
         <v>106</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25">
         <v>77</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25">
         <v>27</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25">
         <v>146</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25">
         <v>906</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="5">
+      <c r="A26">
         <v>77</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26">
         <v>104</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26">
         <v>76</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26">
         <v>26</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26">
         <v>144</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26">
         <v>909</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="5">
+      <c r="A27">
         <v>76</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27">
         <v>102</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27">
         <v>75</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27">
         <v>25</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27">
         <v>142</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27">
         <v>912</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" s="5">
+      <c r="A28">
         <v>75</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28">
         <v>100</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28">
         <v>74</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28">
         <v>24</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28">
         <v>140</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28">
         <v>8</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28">
         <v>915</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="5">
+      <c r="A29">
         <v>74</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29">
         <v>98</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29">
         <v>73</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29">
         <v>138</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29">
         <v>918</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="5">
+      <c r="A30">
         <v>73</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30">
         <v>96</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30">
         <v>72</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30">
         <v>23</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30">
         <v>136</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30">
         <v>7</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30">
         <v>921</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="5">
+      <c r="A31">
         <v>72</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31">
         <v>94</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31">
         <v>71</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31">
         <v>22</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31">
         <v>134</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31">
         <v>924</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="5">
+      <c r="A32">
         <v>71</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32">
         <v>92</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32">
         <v>70</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32">
         <v>21</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32">
         <v>132</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32">
         <v>927</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="5">
+      <c r="A33">
         <v>70</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33">
         <v>90</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33">
         <v>68</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33">
         <v>20</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33">
         <v>130</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33">
         <v>6</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33">
         <v>930</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="5">
+      <c r="A34">
         <v>69</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34">
         <v>88</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34">
         <v>128</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34">
         <v>936</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="5">
+      <c r="A35">
         <v>68</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35">
         <v>86</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35">
         <v>67</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35">
         <v>19</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35">
         <v>126</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35">
         <v>942</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="5">
+      <c r="A36">
         <v>67</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36">
         <v>84</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36">
         <v>66</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36">
         <v>124</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36">
         <v>948</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="5">
+      <c r="A37">
         <v>66</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37">
         <v>82</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37">
         <v>65</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37">
         <v>18</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37">
         <v>122</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37">
         <v>954</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="5">
+      <c r="A38">
         <v>65</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38">
         <v>80</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38">
         <v>64</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38">
         <v>17</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38">
         <v>120</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38">
         <v>5</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38">
         <v>1000</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" s="5">
+      <c r="A39">
         <v>64</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39">
         <v>78</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C39">
         <v>63</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39">
         <v>118</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39">
         <v>1006</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="5">
+      <c r="A40">
         <v>63</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40">
         <v>76</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40">
         <v>62</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40">
         <v>16</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40">
         <v>116</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40">
         <v>1012</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="5">
+      <c r="A41">
         <v>62</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41">
         <v>74</v>
       </c>
-      <c r="C41" s="5">
+      <c r="C41">
         <v>61</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41">
         <v>114</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41">
         <v>1018</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" s="5">
+      <c r="A42">
         <v>61</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42">
         <v>72</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42">
         <v>60</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42">
         <v>15</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42">
         <v>112</v>
       </c>
-      <c r="G42" s="5">
+      <c r="G42">
         <v>1024</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="5">
+      <c r="A43">
         <v>60</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43">
         <v>70</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43">
         <v>58</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43">
         <v>14</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43">
         <v>110</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43">
         <v>4</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43">
         <v>1030</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="5">
+      <c r="A44">
         <v>59</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44">
         <v>68</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44">
         <v>108</v>
       </c>
-      <c r="G44" s="5">
+      <c r="G44">
         <v>1036</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="5">
+      <c r="A45">
         <v>58</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45">
         <v>66</v>
       </c>
-      <c r="C45" s="5">
+      <c r="C45">
         <v>57</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45">
         <v>13</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45">
         <v>106</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45">
         <v>3</v>
       </c>
-      <c r="G45" s="5">
+      <c r="G45">
         <v>1042</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" s="5">
+      <c r="A46">
         <v>57</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46">
         <v>64</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46">
         <v>12</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E46">
         <v>104</v>
       </c>
-      <c r="G46" s="5">
+      <c r="G46">
         <v>1048</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="5">
+      <c r="A47">
         <v>56</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47">
         <v>62</v>
       </c>
-      <c r="C47" s="5">
+      <c r="C47">
         <v>56</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47">
         <v>102</v>
       </c>
-      <c r="G47" s="5">
+      <c r="G47">
         <v>1054</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" s="5">
+      <c r="A48">
         <v>55</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48">
         <v>60</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C48">
         <v>55</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48">
         <v>11</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48">
         <v>100</v>
       </c>
-      <c r="F48" s="5">
+      <c r="F48">
         <v>2</v>
       </c>
-      <c r="G48" s="5">
+      <c r="G48">
         <v>1100</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A49" s="5">
+      <c r="A49">
         <v>54</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49">
         <v>58</v>
       </c>
-      <c r="C49" s="5">
+      <c r="C49">
         <v>53</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49">
         <v>10</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49">
         <v>58</v>
       </c>
-      <c r="G49" s="5">
+      <c r="G49">
         <v>1110</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A50" s="5">
+      <c r="A50">
         <v>53</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50">
         <v>56</v>
       </c>
-      <c r="C50" s="5">
+      <c r="C50">
         <v>51</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50">
         <v>9</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50">
         <v>56</v>
       </c>
-      <c r="G50" s="5">
+      <c r="G50">
         <v>1120</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A51" s="5">
+      <c r="A51">
         <v>52</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51">
         <v>54</v>
       </c>
-      <c r="C51" s="5">
+      <c r="C51">
         <v>50</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51">
         <v>8</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51">
         <v>54</v>
       </c>
-      <c r="G51" s="5">
+      <c r="G51">
         <v>1130</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52" s="5">
+      <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B52">
         <v>52</v>
       </c>
-      <c r="C52" s="5">
+      <c r="C52">
         <v>47</v>
       </c>
-      <c r="D52" s="5">
+      <c r="D52">
         <v>7</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52">
         <v>52</v>
       </c>
-      <c r="G52" s="5">
+      <c r="G52">
         <v>1140</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53" s="5">
+      <c r="A53">
         <v>50</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B53">
         <v>50</v>
       </c>
-      <c r="C53" s="5">
+      <c r="C53">
         <v>46</v>
       </c>
-      <c r="D53" s="5">
+      <c r="D53">
         <v>6</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E53">
         <v>50</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53">
         <v>1</v>
       </c>
-      <c r="G53" s="5">
+      <c r="G53">
         <v>1150</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" s="5">
+      <c r="A54">
         <v>49</v>
       </c>
-      <c r="B54" s="5">
+      <c r="B54">
         <v>48</v>
       </c>
-      <c r="C54" s="5">
+      <c r="C54">
         <v>45</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E54">
         <v>48</v>
       </c>
-      <c r="G54" s="5">
+      <c r="G54">
         <v>1200</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A55" s="5">
+      <c r="A55">
         <v>48</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B55">
         <v>46</v>
       </c>
-      <c r="C55" s="5">
+      <c r="C55">
         <v>44</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D55">
         <v>5</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E55">
         <v>46</v>
       </c>
-      <c r="G55" s="5">
+      <c r="G55">
         <v>1210</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56" s="5">
+      <c r="A56">
         <v>47</v>
       </c>
-      <c r="B56" s="5">
+      <c r="B56">
         <v>44</v>
       </c>
-      <c r="C56" s="5">
+      <c r="C56">
         <v>43</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56">
         <v>44</v>
       </c>
-      <c r="G56" s="5">
+      <c r="G56">
         <v>1220</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A57" s="5">
+      <c r="A57">
         <v>46</v>
       </c>
-      <c r="B57" s="5">
+      <c r="B57">
         <v>42</v>
       </c>
-      <c r="C57" s="5">
+      <c r="C57">
         <v>42</v>
       </c>
-      <c r="D57" s="5">
+      <c r="D57">
         <v>4</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57">
         <v>42</v>
       </c>
-      <c r="G57" s="5">
+      <c r="G57">
         <v>1230</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A58" s="5">
+      <c r="A58">
         <v>45</v>
       </c>
-      <c r="B58" s="5">
+      <c r="B58">
         <v>40</v>
       </c>
-      <c r="C58" s="5">
+      <c r="C58">
         <v>41</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58">
         <v>40</v>
       </c>
-      <c r="G58" s="5">
+      <c r="G58">
         <v>1240</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A59" s="5">
+      <c r="A59">
         <v>44</v>
       </c>
-      <c r="B59" s="5">
+      <c r="B59">
         <v>38</v>
       </c>
-      <c r="C59" s="5">
+      <c r="C59">
         <v>40</v>
       </c>
-      <c r="D59" s="5">
+      <c r="D59">
         <v>3</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59">
         <v>38</v>
       </c>
-      <c r="G59" s="5">
+      <c r="G59">
         <v>1250</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A60" s="5">
+      <c r="A60">
         <v>43</v>
       </c>
-      <c r="B60" s="5">
+      <c r="B60">
         <v>36</v>
       </c>
-      <c r="C60" s="5">
+      <c r="C60">
         <v>37</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60">
         <v>36</v>
       </c>
-      <c r="G60" s="5">
+      <c r="G60">
         <v>1300</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A61" s="5">
+      <c r="A61">
         <v>42</v>
       </c>
-      <c r="B61" s="5">
+      <c r="B61">
         <v>34</v>
       </c>
-      <c r="C61" s="5">
+      <c r="C61">
         <v>36</v>
       </c>
-      <c r="D61" s="5">
+      <c r="D61">
         <v>2</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E61">
         <v>34</v>
       </c>
-      <c r="G61" s="5">
+      <c r="G61">
         <v>1310</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A62" s="5">
+      <c r="A62">
         <v>41</v>
       </c>
-      <c r="B62" s="5">
+      <c r="B62">
         <v>32</v>
       </c>
-      <c r="C62" s="5">
+      <c r="C62">
         <v>35</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E62">
         <v>32</v>
       </c>
-      <c r="G62" s="5">
+      <c r="G62">
         <v>1320</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A63" s="5">
+      <c r="A63">
         <v>40</v>
       </c>
-      <c r="B63" s="5">
+      <c r="B63">
         <v>30</v>
       </c>
-      <c r="C63" s="5">
+      <c r="C63">
         <v>34</v>
       </c>
-      <c r="D63" s="5">
+      <c r="D63">
         <v>1</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E63">
         <v>30</v>
       </c>
-      <c r="G63" s="5">
+      <c r="G63">
         <v>1330</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A64" s="5">
+      <c r="A64">
         <v>0</v>
       </c>
-      <c r="B64" s="5">
+      <c r="B64">
         <v>0</v>
       </c>
-      <c r="C64" s="5">
+      <c r="C64">
         <v>0</v>
       </c>
-      <c r="D64" s="5">
+      <c r="D64">
         <v>0</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E64">
         <v>0</v>
       </c>
-      <c r="F64" s="5">
+      <c r="F64">
         <v>0</v>
       </c>
-      <c r="G64" s="5">
+      <c r="G64">
         <v>0</v>
       </c>
     </row>
@@ -6017,13 +6016,11 @@
   <dimension ref="A2:F64"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="8.7265625" style="5"/>
-    <col min="4" max="4" width="14.90625" style="5" customWidth="1"/>
-    <col min="5" max="16384" width="8.7265625" style="5"/>
+    <col min="4" max="4" width="14.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -6035,7 +6032,7 @@
       <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -6043,1170 +6040,1170 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
+      <c r="A3">
         <v>100</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3">
         <v>140</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3">
         <v>116</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3">
         <v>40</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3">
         <v>225</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3">
         <v>815</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
+      <c r="A4">
         <v>99</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>138</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4">
         <v>113</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4">
         <v>222</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4">
         <v>818</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
+      <c r="A5">
         <v>98</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>136</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5">
         <v>11</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5">
         <v>39</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5">
         <v>219</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5">
         <v>821</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
+      <c r="A6">
         <v>97</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>134</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6">
         <v>107</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6">
         <v>38</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6">
         <v>216</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6">
         <v>824</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
+      <c r="A7">
         <v>96</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>132</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7">
         <v>104</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7">
         <v>37</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7">
         <v>213</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7">
         <v>827</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
+      <c r="A8">
         <v>95</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>130</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8">
         <v>101</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8">
         <v>36</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8">
         <v>210</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8">
         <v>830</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
+      <c r="A9">
         <v>94</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9">
         <v>128</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9">
         <v>99</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9">
         <v>208</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9">
         <v>833</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="5">
+      <c r="A10">
         <v>93</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10">
         <v>126</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10">
         <v>96</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10">
         <v>35</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10">
         <v>206</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10">
         <v>836</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="5">
+      <c r="A11">
         <v>92</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11">
         <v>124</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11">
         <v>92</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11">
         <v>34</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11">
         <v>204</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11">
         <v>839</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="5">
+      <c r="A12">
         <v>91</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12">
         <v>122</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12">
         <v>89</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12">
         <v>33</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12">
         <v>202</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12">
         <v>842</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="5">
+      <c r="A13">
         <v>90</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13">
         <v>120</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13">
         <v>87</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13">
         <v>32</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13">
         <v>200</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13">
         <v>845</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="5">
+      <c r="A14">
         <v>89</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14">
         <v>118</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14">
         <v>86</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14">
         <v>158</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14">
         <v>848</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="5">
+      <c r="A15">
         <v>88</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15">
         <v>116</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15">
         <v>85</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15">
         <v>31</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15">
         <v>156</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15">
         <v>851</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="5">
+      <c r="A16">
         <v>87</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16">
         <v>114</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16">
         <v>83</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16">
         <v>30</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16">
         <v>154</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16">
         <v>854</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="5">
+      <c r="A17">
         <v>86</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17">
         <v>112</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17">
         <v>82</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17">
         <v>29</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17">
         <v>152</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17">
         <v>857</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="5">
+      <c r="A18">
         <v>85</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18">
         <v>110</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18">
         <v>81</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18">
         <v>28</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18">
         <v>150</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18">
         <v>900</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="5">
+      <c r="A19">
         <v>84</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19">
         <v>108</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19">
         <v>79</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19">
         <v>148</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19">
         <v>903</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="5">
+      <c r="A20">
         <v>83</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20">
         <v>106</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20">
         <v>78</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20">
         <v>27</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20">
         <v>146</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20">
         <v>906</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="5">
+      <c r="A21">
         <v>82</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21">
         <v>104</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21">
         <v>77</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21">
         <v>26</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21">
         <v>144</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21">
         <v>909</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="5">
+      <c r="A22">
         <v>81</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22">
         <v>102</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22">
         <v>76</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22">
         <v>25</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22">
         <v>142</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22">
         <v>912</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="5">
+      <c r="A23">
         <v>80</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23">
         <v>100</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23">
         <v>74</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23">
         <v>24</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23">
         <v>140</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23">
         <v>915</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="5">
+      <c r="A24">
         <v>79</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24">
         <v>98</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24">
         <v>73</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24">
         <v>138</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24">
         <v>918</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="5">
+      <c r="A25">
         <v>78</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25">
         <v>96</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25">
         <v>72</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25">
         <v>23</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25">
         <v>136</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25">
         <v>921</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="5">
+      <c r="A26">
         <v>77</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26">
         <v>94</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26">
         <v>71</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26">
         <v>22</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26">
         <v>134</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26">
         <v>924</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="5">
+      <c r="A27">
         <v>76</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27">
         <v>92</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27">
         <v>70</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27">
         <v>21</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27">
         <v>132</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27">
         <v>927</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="5">
+      <c r="A28">
         <v>75</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28">
         <v>90</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28">
         <v>68</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28">
         <v>20</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28">
         <v>130</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28">
         <v>930</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="5">
+      <c r="A29">
         <v>74</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29">
         <v>88</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29">
         <v>67</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29">
         <v>128</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29">
         <v>933</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="5">
+      <c r="A30">
         <v>73</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30">
         <v>86</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30">
         <v>66</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30">
         <v>19</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30">
         <v>126</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30">
         <v>936</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="5">
+      <c r="A31">
         <v>72</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31">
         <v>84</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31">
         <v>65</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31">
         <v>124</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31">
         <v>939</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="5">
+      <c r="A32">
         <v>71</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32">
         <v>82</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32">
         <v>64</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32">
         <v>18</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32">
         <v>122</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32">
         <v>942</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="5">
+      <c r="A33">
         <v>70</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33">
         <v>80</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33">
         <v>63</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33">
         <v>17</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33">
         <v>120</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33">
         <v>945</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="5">
+      <c r="A34">
         <v>69</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34">
         <v>78</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34">
         <v>62</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34">
         <v>118</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34">
         <v>951</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="5">
+      <c r="A35">
         <v>68</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35">
         <v>76</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35">
         <v>61</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35">
         <v>16</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35">
         <v>116</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35">
         <v>957</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="5">
+      <c r="A36">
         <v>67</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36">
         <v>74</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36">
         <v>60</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36">
         <v>114</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36">
         <v>1003</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="5">
+      <c r="A37">
         <v>66</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37">
         <v>72</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37">
         <v>58</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37">
         <v>15</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37">
         <v>112</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37">
         <v>1009</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="5">
+      <c r="A38">
         <v>65</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38">
         <v>70</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38">
         <v>57</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38">
         <v>14</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38">
         <v>110</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38">
         <v>1015</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="5">
+      <c r="A39">
         <v>64</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39">
         <v>68</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39">
         <v>108</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39">
         <v>1021</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="5">
+      <c r="A40">
         <v>63</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40">
         <v>66</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40">
         <v>56</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40">
         <v>13</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40">
         <v>106</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40">
         <v>1027</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="5">
+      <c r="A41">
         <v>62</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41">
         <v>64</v>
       </c>
-      <c r="C41" s="5">
+      <c r="C41">
         <v>55</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41">
         <v>104</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41">
         <v>1033</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="5">
+      <c r="A42">
         <v>61</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42">
         <v>62</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42">
         <v>54</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42">
         <v>12</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42">
         <v>102</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42">
         <v>1039</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="5">
+      <c r="A43">
         <v>60</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43">
         <v>60</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43">
         <v>53</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43">
         <v>11</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43">
         <v>100</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43">
         <v>1045</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="5">
+      <c r="A44">
         <v>59</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44">
         <v>58</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44">
         <v>58</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44">
         <v>1051</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="5">
+      <c r="A45">
         <v>58</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45">
         <v>56</v>
       </c>
-      <c r="C45" s="5">
+      <c r="C45">
         <v>52</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45">
         <v>10</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45">
         <v>56</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45">
         <v>1057</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="5">
+      <c r="A46">
         <v>57</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46">
         <v>54</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E46">
         <v>54</v>
       </c>
-      <c r="F46" s="5">
+      <c r="F46">
         <v>1103</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="5">
+      <c r="A47">
         <v>56</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47">
         <v>52</v>
       </c>
-      <c r="C47" s="5">
+      <c r="C47">
         <v>51</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47">
         <v>52</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47">
         <v>1109</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="5">
+      <c r="A48">
         <v>55</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48">
         <v>50</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C48">
         <v>50</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48">
         <v>9</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48">
         <v>50</v>
       </c>
-      <c r="F48" s="5">
+      <c r="F48">
         <v>1115</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="5">
+      <c r="A49">
         <v>54</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49">
         <v>48</v>
       </c>
-      <c r="C49" s="5">
+      <c r="C49">
         <v>47</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49">
         <v>48</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F49">
         <v>1121</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" s="5">
+      <c r="A50">
         <v>53</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50">
         <v>46</v>
       </c>
-      <c r="C50" s="5">
+      <c r="C50">
         <v>46</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50">
         <v>46</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F50">
         <v>1127</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" s="5">
+      <c r="A51">
         <v>52</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51">
         <v>44</v>
       </c>
-      <c r="C51" s="5">
+      <c r="C51">
         <v>45</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51">
         <v>8</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51">
         <v>44</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F51">
         <v>1133</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A52" s="5">
+      <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B52">
         <v>42</v>
       </c>
-      <c r="C52" s="5">
+      <c r="C52">
         <v>44</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52">
         <v>42</v>
       </c>
-      <c r="F52" s="5">
+      <c r="F52">
         <v>1139</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A53" s="5">
+      <c r="A53">
         <v>50</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B53">
         <v>40</v>
       </c>
-      <c r="C53" s="5">
+      <c r="C53">
         <v>43</v>
       </c>
-      <c r="D53" s="5">
+      <c r="D53">
         <v>7</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E53">
         <v>40</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53">
         <v>1145</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A54" s="5">
+      <c r="A54">
         <v>49</v>
       </c>
-      <c r="B54" s="5">
+      <c r="B54">
         <v>38</v>
       </c>
-      <c r="C54" s="5">
+      <c r="C54">
         <v>42</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E54">
         <v>38</v>
       </c>
-      <c r="F54" s="5">
+      <c r="F54">
         <v>1151</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A55" s="5">
+      <c r="A55">
         <v>48</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B55">
         <v>36</v>
       </c>
-      <c r="C55" s="5">
+      <c r="C55">
         <v>41</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D55">
         <v>6</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E55">
         <v>36</v>
       </c>
-      <c r="F55" s="5">
+      <c r="F55">
         <v>1157</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A56" s="5">
+      <c r="A56">
         <v>47</v>
       </c>
-      <c r="B56" s="5">
+      <c r="B56">
         <v>34</v>
       </c>
-      <c r="C56" s="5">
+      <c r="C56">
         <v>40</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56">
         <v>34</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F56">
         <v>1203</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" s="5">
+      <c r="A57">
         <v>46</v>
       </c>
-      <c r="B57" s="5">
+      <c r="B57">
         <v>32</v>
       </c>
-      <c r="C57" s="5">
+      <c r="C57">
         <v>37</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57">
         <v>32</v>
       </c>
-      <c r="F57" s="5">
+      <c r="F57">
         <v>1209</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A58" s="5">
+      <c r="A58">
         <v>45</v>
       </c>
-      <c r="B58" s="5">
+      <c r="B58">
         <v>30</v>
       </c>
-      <c r="C58" s="5">
+      <c r="C58">
         <v>36</v>
       </c>
-      <c r="D58" s="5">
+      <c r="D58">
         <v>5</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58">
         <v>30</v>
       </c>
-      <c r="F58" s="5">
+      <c r="F58">
         <v>1215</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A59" s="5">
+      <c r="A59">
         <v>44</v>
       </c>
-      <c r="B59" s="5">
+      <c r="B59">
         <v>28</v>
       </c>
-      <c r="C59" s="5">
+      <c r="C59">
         <v>35</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59">
         <v>28</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F59">
         <v>1221</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A60" s="5">
+      <c r="A60">
         <v>43</v>
       </c>
-      <c r="B60" s="5">
+      <c r="B60">
         <v>26</v>
       </c>
-      <c r="C60" s="5">
+      <c r="C60">
         <v>34</v>
       </c>
-      <c r="D60" s="5">
+      <c r="D60">
         <v>4</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60">
         <v>26</v>
       </c>
-      <c r="F60" s="5">
+      <c r="F60">
         <v>1227</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A61" s="5">
+      <c r="A61">
         <v>42</v>
       </c>
-      <c r="B61" s="5">
+      <c r="B61">
         <v>24</v>
       </c>
-      <c r="C61" s="5">
+      <c r="C61">
         <v>33</v>
       </c>
-      <c r="D61" s="5">
+      <c r="D61">
         <v>3</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E61">
         <v>24</v>
       </c>
-      <c r="F61" s="5">
+      <c r="F61">
         <v>1233</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62" s="5">
+      <c r="A62">
         <v>41</v>
       </c>
-      <c r="B62" s="5">
+      <c r="B62">
         <v>22</v>
       </c>
-      <c r="C62" s="5">
+      <c r="C62">
         <v>32</v>
       </c>
-      <c r="D62" s="5">
+      <c r="D62">
         <v>2</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E62">
         <v>22</v>
       </c>
-      <c r="F62" s="5">
+      <c r="F62">
         <v>1239</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A63" s="5">
+      <c r="A63">
         <v>40</v>
       </c>
-      <c r="B63" s="5">
+      <c r="B63">
         <v>20</v>
       </c>
-      <c r="C63" s="5">
+      <c r="C63">
         <v>30</v>
       </c>
-      <c r="D63" s="5">
+      <c r="D63">
         <v>1</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E63">
         <v>20</v>
       </c>
-      <c r="F63" s="5">
+      <c r="F63">
         <v>1245</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A64" s="5">
+      <c r="A64">
         <v>0</v>
       </c>
-      <c r="B64" s="5">
+      <c r="B64">
         <v>0</v>
       </c>
-      <c r="C64" s="5">
+      <c r="C64">
         <v>0</v>
       </c>
-      <c r="D64" s="5">
+      <c r="D64">
         <v>0</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E64">
         <v>0</v>
       </c>
-      <c r="F64" s="5">
+      <c r="F64">
         <v>0</v>
       </c>
     </row>
@@ -7226,1176 +7223,1175 @@
   <dimension ref="A2:F64"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.1796875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="8.08984375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="7.26953125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="14.453125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="8.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="8.7265625" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="8.7265625" style="5"/>
+    <col min="1" max="1" width="5.1796875" customWidth="1"/>
+    <col min="2" max="2" width="8.08984375" customWidth="1"/>
+    <col min="3" max="3" width="7.26953125" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" customWidth="1"/>
+    <col min="5" max="5" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
+      <c r="A3">
         <v>100</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3">
         <v>130</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3">
         <v>109</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3">
         <v>36</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3">
         <v>215</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3">
         <v>600</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
+      <c r="A4">
         <v>99</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>128</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4">
         <v>105</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4">
         <v>212</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4">
         <v>603</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
+      <c r="A5">
         <v>98</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>126</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5">
         <v>102</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5">
         <v>35</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5">
         <v>209</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5">
         <v>606</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
+      <c r="A6">
         <v>97</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>124</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6">
         <v>99</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6">
         <v>34</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6">
         <v>206</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6">
         <v>609</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
+      <c r="A7">
         <v>96</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>122</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7">
         <v>96</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7">
         <v>33</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7">
         <v>203</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7">
         <v>612</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
+      <c r="A8">
         <v>95</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>120</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8">
         <v>92</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8">
         <v>32</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8">
         <v>200</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8">
         <v>615</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
+      <c r="A9">
         <v>94</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9">
         <v>118</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9">
         <v>90</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9">
         <v>158</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9">
         <v>618</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="5">
+      <c r="A10">
         <v>93</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10">
         <v>116</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10">
         <v>89</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10">
         <v>31</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10">
         <v>156</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10">
         <v>621</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="5">
+      <c r="A11">
         <v>92</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11">
         <v>114</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11">
         <v>87</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11">
         <v>30</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11">
         <v>154</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11">
         <v>624</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="5">
+      <c r="A12">
         <v>91</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12">
         <v>112</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12">
         <v>86</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12">
         <v>29</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12">
         <v>152</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12">
         <v>627</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="5">
+      <c r="A13">
         <v>90</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13">
         <v>110</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13">
         <v>84</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13">
         <v>28</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13">
         <v>150</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13">
         <v>630</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="5">
+      <c r="A14">
         <v>89</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14">
         <v>108</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14">
         <v>82</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14">
         <v>148</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14">
         <v>633</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="5">
+      <c r="A15">
         <v>88</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15">
         <v>106</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15">
         <v>81</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15">
         <v>27</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15">
         <v>146</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15">
         <v>636</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="5">
+      <c r="A16">
         <v>87</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16">
         <v>104</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16">
         <v>80</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16">
         <v>26</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16">
         <v>144</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16">
         <v>639</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="5">
+      <c r="A17">
         <v>86</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17">
         <v>102</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17">
         <v>79</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17">
         <v>25</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17">
         <v>142</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17">
         <v>642</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="5">
+      <c r="A18">
         <v>85</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18">
         <v>100</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18">
         <v>77</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18">
         <v>24</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18">
         <v>140</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18">
         <v>645</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="5">
+      <c r="A19">
         <v>84</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19">
         <v>98</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19">
         <v>76</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19">
         <v>138</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19">
         <v>648</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="5">
+      <c r="A20">
         <v>83</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20">
         <v>96</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20">
         <v>75</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20">
         <v>23</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20">
         <v>136</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20">
         <v>651</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="5">
+      <c r="A21">
         <v>82</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21">
         <v>94</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21">
         <v>73</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21">
         <v>22</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21">
         <v>134</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21">
         <v>654</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="5">
+      <c r="A22">
         <v>81</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22">
         <v>92</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22">
         <v>72</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22">
         <v>21</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22">
         <v>132</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22">
         <v>657</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="5">
+      <c r="A23">
         <v>80</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23">
         <v>90</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23">
         <v>71</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23">
         <v>20</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23">
         <v>130</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23">
         <v>700</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="5">
+      <c r="A24">
         <v>79</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24">
         <v>88</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24">
         <v>70</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24">
         <v>128</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24">
         <v>703</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="5">
+      <c r="A25">
         <v>78</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25">
         <v>86</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25">
         <v>68</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25">
         <v>19</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25">
         <v>126</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25">
         <v>706</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="5">
+      <c r="A26">
         <v>77</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26">
         <v>84</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26">
         <v>67</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26">
         <v>124</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26">
         <v>709</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="5">
+      <c r="A27">
         <v>76</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27">
         <v>82</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27">
         <v>66</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27">
         <v>18</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27">
         <v>122</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27">
         <v>712</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="5">
+      <c r="A28">
         <v>75</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28">
         <v>80</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28">
         <v>65</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28">
         <v>17</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28">
         <v>120</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28">
         <v>715</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="5">
+      <c r="A29">
         <v>74</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29">
         <v>78</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29">
         <v>64</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29">
         <v>118</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29">
         <v>718</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="5">
+      <c r="A30">
         <v>73</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30">
         <v>76</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30">
         <v>63</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30">
         <v>16</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30">
         <v>116</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30">
         <v>721</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="5">
+      <c r="A31">
         <v>72</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31">
         <v>74</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31">
         <v>61</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31">
         <v>114</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31">
         <v>724</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="5">
+      <c r="A32">
         <v>71</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32">
         <v>72</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32">
         <v>60</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32">
         <v>15</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32">
         <v>112</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32">
         <v>727</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="5">
+      <c r="A33">
         <v>70</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33">
         <v>70</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33">
         <v>58</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33">
         <v>14</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33">
         <v>110</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33">
         <v>730</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="5">
+      <c r="A34">
         <v>69</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34">
         <v>68</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34">
         <v>108</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34">
         <v>736</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="5">
+      <c r="A35">
         <v>68</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35">
         <v>66</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35">
         <v>57</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35">
         <v>13</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35">
         <v>106</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35">
         <v>742</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="5">
+      <c r="A36">
         <v>67</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36">
         <v>64</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36">
         <v>56</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36">
         <v>104</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36">
         <v>748</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="5">
+      <c r="A37">
         <v>66</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37">
         <v>62</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37">
         <v>55</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37">
         <v>12</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37">
         <v>102</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37">
         <v>754</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="5">
+      <c r="A38">
         <v>65</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38">
         <v>60</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38">
         <v>54</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38">
         <v>11</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38">
         <v>100</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38">
         <v>800</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="5">
+      <c r="A39">
         <v>64</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39">
         <v>58</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39">
         <v>58</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39">
         <v>806</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="5">
+      <c r="A40">
         <v>63</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40">
         <v>56</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40">
         <v>53</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40">
         <v>56</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40">
         <v>812</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="5">
+      <c r="A41">
         <v>62</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41">
         <v>54</v>
       </c>
-      <c r="C41" s="5">
+      <c r="C41">
         <v>52</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41">
         <v>10</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41">
         <v>54</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41">
         <v>818</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="5">
+      <c r="A42">
         <v>61</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42">
         <v>52</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42">
         <v>51</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42">
         <v>52</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42">
         <v>824</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="5">
+      <c r="A43">
         <v>60</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43">
         <v>50</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43">
         <v>50</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43">
         <v>9</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43">
         <v>50</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43">
         <v>830</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="5">
+      <c r="A44">
         <v>59</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44">
         <v>48</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44">
         <v>48</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44">
         <v>836</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="5">
+      <c r="A45">
         <v>58</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45">
         <v>46</v>
       </c>
-      <c r="C45" s="5">
+      <c r="C45">
         <v>47</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45">
         <v>46</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45">
         <v>842</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="5">
+      <c r="A46">
         <v>57</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46">
         <v>44</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E46">
         <v>44</v>
       </c>
-      <c r="F46" s="5">
+      <c r="F46">
         <v>848</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="5">
+      <c r="A47">
         <v>56</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47">
         <v>42</v>
       </c>
-      <c r="C47" s="5">
+      <c r="C47">
         <v>46</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47">
         <v>42</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47">
         <v>854</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="5">
+      <c r="A48">
         <v>55</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48">
         <v>40</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C48">
         <v>45</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48">
         <v>8</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48">
         <v>40</v>
       </c>
-      <c r="F48" s="5">
+      <c r="F48">
         <v>900</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="5">
+      <c r="A49">
         <v>54</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49">
         <v>38</v>
       </c>
-      <c r="C49" s="5">
+      <c r="C49">
         <v>44</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49">
         <v>38</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F49">
         <v>906</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" s="5">
+      <c r="A50">
         <v>53</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50">
         <v>36</v>
       </c>
-      <c r="C50" s="5">
+      <c r="C50">
         <v>43</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50">
         <v>36</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F50">
         <v>912</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" s="5">
+      <c r="A51">
         <v>52</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51">
         <v>34</v>
       </c>
-      <c r="C51" s="5">
+      <c r="C51">
         <v>42</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51">
         <v>7</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51">
         <v>34</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F51">
         <v>918</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A52" s="5">
+      <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B52">
         <v>32</v>
       </c>
-      <c r="C52" s="5">
+      <c r="C52">
         <v>41</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52">
         <v>32</v>
       </c>
-      <c r="F52" s="5">
+      <c r="F52">
         <v>924</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A53" s="5">
+      <c r="A53">
         <v>50</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B53">
         <v>30</v>
       </c>
-      <c r="C53" s="5">
+      <c r="C53">
         <v>40</v>
       </c>
-      <c r="D53" s="5">
+      <c r="D53">
         <v>6</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E53">
         <v>30</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53">
         <v>930</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A54" s="5">
+      <c r="A54">
         <v>49</v>
       </c>
-      <c r="B54" s="5">
+      <c r="B54">
         <v>28</v>
       </c>
-      <c r="C54" s="5">
+      <c r="C54">
         <v>37</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E54">
         <v>28</v>
       </c>
-      <c r="F54" s="5">
+      <c r="F54">
         <v>936</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A55" s="5">
+      <c r="A55">
         <v>48</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B55">
         <v>26</v>
       </c>
-      <c r="C55" s="5">
+      <c r="C55">
         <v>36</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D55">
         <v>5</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E55">
         <v>26</v>
       </c>
-      <c r="F55" s="5">
+      <c r="F55">
         <v>942</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A56" s="5">
+      <c r="A56">
         <v>47</v>
       </c>
-      <c r="B56" s="5">
+      <c r="B56">
         <v>24</v>
       </c>
-      <c r="C56" s="5">
+      <c r="C56">
         <v>35</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56">
         <v>24</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F56">
         <v>948</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" s="5">
+      <c r="A57">
         <v>46</v>
       </c>
-      <c r="B57" s="5">
+      <c r="B57">
         <v>22</v>
       </c>
-      <c r="C57" s="5">
+      <c r="C57">
         <v>34</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57">
         <v>22</v>
       </c>
-      <c r="F57" s="5">
+      <c r="F57">
         <v>954</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A58" s="5">
+      <c r="A58">
         <v>45</v>
       </c>
-      <c r="B58" s="5">
+      <c r="B58">
         <v>20</v>
       </c>
-      <c r="C58" s="5">
+      <c r="C58">
         <v>33</v>
       </c>
-      <c r="D58" s="5">
+      <c r="D58">
         <v>4</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58">
         <v>20</v>
       </c>
-      <c r="F58" s="5">
+      <c r="F58">
         <v>1000</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A59" s="5">
+      <c r="A59">
         <v>44</v>
       </c>
-      <c r="B59" s="5">
+      <c r="B59">
         <v>18</v>
       </c>
-      <c r="C59" s="5">
+      <c r="C59">
         <v>32</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59">
         <v>18</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F59">
         <v>1006</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A60" s="5">
+      <c r="A60">
         <v>43</v>
       </c>
-      <c r="B60" s="5">
+      <c r="B60">
         <v>16</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60">
         <v>16</v>
       </c>
-      <c r="F60" s="5">
+      <c r="F60">
         <v>1012</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A61" s="5">
+      <c r="A61">
         <v>42</v>
       </c>
-      <c r="B61" s="5">
+      <c r="B61">
         <v>14</v>
       </c>
-      <c r="C61" s="5">
+      <c r="C61">
         <v>31</v>
       </c>
-      <c r="D61" s="5">
+      <c r="D61">
         <v>3</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E61">
         <v>14</v>
       </c>
-      <c r="F61" s="5">
+      <c r="F61">
         <v>1018</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62" s="5">
+      <c r="A62">
         <v>41</v>
       </c>
-      <c r="B62" s="5">
+      <c r="B62">
         <v>12</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E62">
         <v>12</v>
       </c>
-      <c r="F62" s="5">
+      <c r="F62">
         <v>1024</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A63" s="5">
+      <c r="A63">
         <v>40</v>
       </c>
-      <c r="B63" s="5">
+      <c r="B63">
         <v>10</v>
       </c>
-      <c r="C63" s="5">
+      <c r="C63">
         <v>30</v>
       </c>
-      <c r="D63" s="5">
+      <c r="D63">
         <v>2</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E63">
         <v>10</v>
       </c>
-      <c r="F63" s="5">
+      <c r="F63">
         <v>1030</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A64" s="5">
+      <c r="A64">
         <v>0</v>
       </c>
-      <c r="B64" s="5">
+      <c r="B64">
         <v>0</v>
       </c>
-      <c r="C64" s="5">
+      <c r="C64">
         <v>0</v>
       </c>
-      <c r="D64" s="5">
+      <c r="D64">
         <v>0</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E64">
         <v>0</v>
       </c>
-      <c r="F64" s="5">
+      <c r="F64">
         <v>0</v>
       </c>
     </row>
@@ -8412,11 +8408,11 @@
   <conditionalFormatting sqref="C24:C27">
     <cfRule type="duplicateValues" dxfId="6" priority="5"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C29:C32">
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E21 C19:C22">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C29:C32">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -8430,1139 +8426,1174 @@
   <dimension ref="A2:F64"/>
   <sheetFormatPr defaultColWidth="12.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="12.453125" style="5"/>
+    <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
+      <c r="A3">
         <v>100</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3">
         <v>120</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3">
         <v>98</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3">
         <v>28</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3">
         <v>200</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3">
         <v>630</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
+      <c r="A4">
         <v>99</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>118</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4">
         <v>97</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4">
         <v>158</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4">
         <v>633</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
+      <c r="A5">
         <v>98</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>116</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5">
         <v>95</v>
       </c>
-      <c r="E5" s="5">
+      <c r="D5">
+        <v>27</v>
+      </c>
+      <c r="E5">
         <v>156</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5">
         <v>636</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
+      <c r="A6">
         <v>97</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>114</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6">
         <v>93</v>
       </c>
-      <c r="E6" s="5">
+      <c r="D6">
+        <v>26</v>
+      </c>
+      <c r="E6">
         <v>154</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6">
         <v>639</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
+      <c r="A7">
         <v>96</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>112</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7">
         <v>91</v>
       </c>
-      <c r="E7" s="5">
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
         <v>152</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7">
         <v>642</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
+      <c r="A8">
         <v>95</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>110</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8">
         <v>89</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8">
         <v>24</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8">
         <v>150</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8">
         <v>645</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
+      <c r="A9">
         <v>94</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9">
         <v>108</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9">
         <v>87</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9">
         <v>148</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9">
         <v>648</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="5">
+      <c r="A10">
         <v>93</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10">
         <v>106</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10">
         <v>86</v>
       </c>
-      <c r="E10" s="5">
+      <c r="D10">
+        <v>23</v>
+      </c>
+      <c r="E10">
         <v>146</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10">
         <v>651</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="5">
+      <c r="A11">
         <v>92</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11">
         <v>104</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11">
         <v>84</v>
       </c>
-      <c r="E11" s="5">
+      <c r="D11">
+        <v>22</v>
+      </c>
+      <c r="E11">
         <v>144</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11">
         <v>654</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="5">
+      <c r="A12">
         <v>91</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12">
         <v>102</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12">
         <v>83</v>
       </c>
-      <c r="E12" s="5">
+      <c r="D12">
+        <v>21</v>
+      </c>
+      <c r="E12">
         <v>142</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12">
         <v>657</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="5">
+      <c r="A13">
         <v>90</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13">
         <v>100</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13">
         <v>81</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13">
         <v>20</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13">
         <v>140</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13">
         <v>700</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="5">
+      <c r="A14">
         <v>89</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14">
         <v>98</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14">
         <v>79</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14">
         <v>138</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14">
         <v>703</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="5">
+      <c r="A15">
         <v>88</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15">
         <v>96</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15">
         <v>77</v>
       </c>
-      <c r="E15" s="5">
+      <c r="D15">
+        <v>19</v>
+      </c>
+      <c r="E15">
         <v>136</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15">
         <v>706</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="5">
+      <c r="A16">
         <v>87</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16">
         <v>94</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16">
         <v>78</v>
       </c>
-      <c r="E16" s="5">
+      <c r="D16">
+        <v>18</v>
+      </c>
+      <c r="E16">
         <v>134</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16">
         <v>709</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="5">
+      <c r="A17">
         <v>86</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17">
         <v>92</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17">
         <v>76</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17">
         <v>132</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17">
         <v>712</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="5">
+      <c r="A18">
         <v>85</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18">
         <v>90</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18">
         <v>74</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18">
         <v>17</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18">
         <v>130</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18">
         <v>715</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="5">
+      <c r="A19">
         <v>84</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19">
         <v>88</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19">
         <v>73</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19">
         <v>128</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19">
         <v>718</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="5">
+      <c r="A20">
         <v>83</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20">
         <v>86</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20">
         <v>72</v>
       </c>
-      <c r="E20" s="5">
+      <c r="D20">
+        <v>16</v>
+      </c>
+      <c r="E20">
         <v>126</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20">
         <v>721</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="5">
+      <c r="A21">
         <v>82</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21">
         <v>84</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21">
         <v>70</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21">
         <v>124</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21">
         <v>724</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="5">
+      <c r="A22">
         <v>81</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22">
         <v>82</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22">
         <v>68</v>
       </c>
-      <c r="E22" s="5">
+      <c r="D22">
+        <v>15</v>
+      </c>
+      <c r="E22">
         <v>122</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22">
         <v>727</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="5">
+      <c r="A23">
         <v>80</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23">
         <v>80</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23">
         <v>67</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23">
         <v>14</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23">
         <v>120</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23">
         <v>730</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="5">
+      <c r="A24">
         <v>79</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24">
         <v>78</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24">
         <v>66</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24">
         <v>118</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24">
         <v>733</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="5">
+      <c r="A25">
         <v>78</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25">
         <v>76</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25">
         <v>65</v>
       </c>
-      <c r="E25" s="5">
+      <c r="D25">
+        <v>13</v>
+      </c>
+      <c r="E25">
         <v>116</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25">
         <v>736</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="5">
+      <c r="A26">
         <v>77</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26">
         <v>74</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26">
         <v>64</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26">
         <v>114</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26">
         <v>739</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="5">
+      <c r="A27">
         <v>76</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27">
         <v>72</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27">
         <v>63</v>
       </c>
-      <c r="E27" s="5">
+      <c r="D27">
+        <v>12</v>
+      </c>
+      <c r="E27">
         <v>112</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27">
         <v>742</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="5">
+      <c r="A28">
         <v>75</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28">
         <v>70</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28">
         <v>62</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28">
         <v>11</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28">
         <v>110</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28">
         <v>745</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="5">
+      <c r="A29">
         <v>74</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29">
         <v>68</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29">
         <v>61</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29">
         <v>108</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29">
         <v>748</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="5">
+      <c r="A30">
         <v>73</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30">
         <v>66</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30">
         <v>60</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30">
         <v>106</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30">
         <v>751</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="5">
+      <c r="A31">
         <v>72</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31">
         <v>64</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31">
         <v>57</v>
       </c>
-      <c r="E31" s="5">
+      <c r="D31">
+        <v>10</v>
+      </c>
+      <c r="E31">
         <v>104</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31">
         <v>754</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="5">
+      <c r="A32">
         <v>71</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32">
         <v>62</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32">
         <v>56</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32">
         <v>102</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32">
         <v>757</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="5">
+      <c r="A33">
         <v>70</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33">
         <v>60</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33">
         <v>55</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33">
         <v>9</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33">
         <v>100</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33">
         <v>800</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="5">
+      <c r="A34">
         <v>69</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34">
         <v>58</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34">
         <v>58</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34">
         <v>806</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="5">
+      <c r="A35">
         <v>68</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35">
         <v>56</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35">
         <v>54</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35">
         <v>56</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35">
         <v>812</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="5">
+      <c r="A36">
         <v>67</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36">
         <v>54</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36">
         <v>53</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36">
         <v>54</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36">
         <v>818</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="5">
+      <c r="A37">
         <v>66</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37">
         <v>52</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37">
         <v>52</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37">
         <v>52</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37">
         <v>824</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="5">
+      <c r="A38">
         <v>65</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38">
         <v>50</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38">
         <v>51</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38">
         <v>8</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38">
         <v>50</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38">
         <v>830</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="5">
+      <c r="A39">
         <v>64</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39">
         <v>48</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39">
         <v>48</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39">
         <v>836</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="5">
+      <c r="A40">
         <v>63</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40">
         <v>46</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40">
         <v>50</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40">
         <v>46</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40">
         <v>842</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="5">
+      <c r="A41">
         <v>62</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41">
         <v>44</v>
       </c>
-      <c r="C41" s="5">
+      <c r="C41">
         <v>47</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41">
         <v>44</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41">
         <v>848</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="5">
+      <c r="A42">
         <v>61</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42">
         <v>42</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42">
         <v>46</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42">
         <v>42</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42">
         <v>854</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="5">
+      <c r="A43">
         <v>60</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43">
         <v>40</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43">
         <v>45</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43">
         <v>7</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43">
         <v>40</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43">
         <v>900</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="5">
+      <c r="A44">
         <v>59</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44">
         <v>38</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44">
         <v>38</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44">
         <v>906</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="5">
+      <c r="A45">
         <v>58</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45">
         <v>36</v>
       </c>
-      <c r="C45" s="5">
+      <c r="C45">
         <v>44</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45">
         <v>36</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45">
         <v>912</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="5">
+      <c r="A46">
         <v>57</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46">
         <v>34</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E46">
         <v>34</v>
       </c>
-      <c r="F46" s="5">
+      <c r="F46">
         <v>918</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="5">
+      <c r="A47">
         <v>56</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47">
         <v>32</v>
       </c>
-      <c r="C47" s="5">
+      <c r="C47">
         <v>43</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47">
         <v>32</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47">
         <v>924</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="5">
+      <c r="A48">
         <v>55</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48">
         <v>30</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C48">
         <v>42</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48">
         <v>6</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48">
         <v>30</v>
       </c>
-      <c r="F48" s="5">
+      <c r="F48">
         <v>930</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="5">
+      <c r="A49">
         <v>54</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49">
         <v>28</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C49" s="6">
         <v>41</v>
       </c>
-      <c r="D49" s="5">
+      <c r="E49">
+        <v>28</v>
+      </c>
+      <c r="F49">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>53</v>
+      </c>
+      <c r="B50">
+        <v>26</v>
+      </c>
+      <c r="C50">
+        <v>40</v>
+      </c>
+      <c r="E50">
+        <v>26</v>
+      </c>
+      <c r="F50">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>52</v>
+      </c>
+      <c r="B51">
+        <v>24</v>
+      </c>
+      <c r="C51">
+        <v>37</v>
+      </c>
+      <c r="D51">
+        <v>5</v>
+      </c>
+      <c r="E51">
+        <v>24</v>
+      </c>
+      <c r="F51">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>22</v>
+      </c>
+      <c r="C52">
+        <v>36</v>
+      </c>
+      <c r="E52">
+        <v>22</v>
+      </c>
+      <c r="F52">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>50</v>
+      </c>
+      <c r="B53">
+        <v>20</v>
+      </c>
+      <c r="C53">
+        <v>35</v>
+      </c>
+      <c r="D53">
+        <v>4</v>
+      </c>
+      <c r="E53">
+        <v>20</v>
+      </c>
+      <c r="F53">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>49</v>
+      </c>
+      <c r="B54">
+        <v>18</v>
+      </c>
+      <c r="C54">
+        <v>34</v>
+      </c>
+      <c r="E54">
+        <v>18</v>
+      </c>
+      <c r="F54">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>48</v>
+      </c>
+      <c r="B55">
+        <v>16</v>
+      </c>
+      <c r="C55">
+        <v>33</v>
+      </c>
+      <c r="E55">
+        <v>16</v>
+      </c>
+      <c r="F55">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>47</v>
+      </c>
+      <c r="B56">
+        <v>14</v>
+      </c>
+      <c r="C56">
+        <v>32</v>
+      </c>
+      <c r="D56">
+        <v>3</v>
+      </c>
+      <c r="E56">
+        <v>14</v>
+      </c>
+      <c r="F56">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>46</v>
+      </c>
+      <c r="B57">
+        <v>12</v>
+      </c>
+      <c r="C57">
+        <v>31</v>
+      </c>
+      <c r="E57">
+        <v>12</v>
+      </c>
+      <c r="F57">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>45</v>
+      </c>
+      <c r="B58">
+        <v>10</v>
+      </c>
+      <c r="C58">
+        <v>30</v>
+      </c>
+      <c r="E58">
+        <v>10</v>
+      </c>
+      <c r="F58">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>44</v>
+      </c>
+      <c r="B59">
+        <v>8</v>
+      </c>
+      <c r="C59">
+        <v>27</v>
+      </c>
+      <c r="D59">
+        <v>2</v>
+      </c>
+      <c r="E59">
+        <v>8</v>
+      </c>
+      <c r="F59">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>43</v>
+      </c>
+      <c r="B60">
+        <v>6</v>
+      </c>
+      <c r="C60">
+        <v>26</v>
+      </c>
+      <c r="E60">
+        <v>6</v>
+      </c>
+      <c r="F60">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>42</v>
+      </c>
+      <c r="B61">
+        <v>4</v>
+      </c>
+      <c r="C61">
+        <v>25</v>
+      </c>
+      <c r="E61">
+        <v>4</v>
+      </c>
+      <c r="F61">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>41</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62">
+        <v>24</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="F62">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>40</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63">
+        <v>20</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64">
         <v>0</v>
       </c>
-      <c r="E49" s="5">
-        <v>28</v>
-      </c>
-      <c r="F49" s="5">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" s="5">
-        <v>53</v>
-      </c>
-      <c r="B50" s="5">
-        <v>26</v>
-      </c>
-      <c r="C50" s="5">
-        <v>40</v>
-      </c>
-      <c r="E50" s="5">
-        <v>26</v>
-      </c>
-      <c r="F50" s="5">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" s="5">
-        <v>52</v>
-      </c>
-      <c r="B51" s="5">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>37</v>
-      </c>
-      <c r="D51" s="5">
-        <v>5</v>
-      </c>
-      <c r="E51" s="5">
-        <v>24</v>
-      </c>
-      <c r="F51" s="5">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A52" s="5">
-        <v>51</v>
-      </c>
-      <c r="B52" s="5">
-        <v>22</v>
-      </c>
-      <c r="C52" s="5">
-        <v>36</v>
-      </c>
-      <c r="E52" s="5">
-        <v>22</v>
-      </c>
-      <c r="F52" s="5">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A53" s="5">
-        <v>50</v>
-      </c>
-      <c r="B53" s="5">
-        <v>20</v>
-      </c>
-      <c r="C53" s="5">
-        <v>35</v>
-      </c>
-      <c r="D53" s="5">
-        <v>4</v>
-      </c>
-      <c r="E53" s="5">
-        <v>20</v>
-      </c>
-      <c r="F53" s="5">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A54" s="5">
-        <v>49</v>
-      </c>
-      <c r="B54" s="5">
-        <v>18</v>
-      </c>
-      <c r="C54" s="5">
-        <v>34</v>
-      </c>
-      <c r="E54" s="5">
-        <v>18</v>
-      </c>
-      <c r="F54" s="5">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A55" s="5">
-        <v>48</v>
-      </c>
-      <c r="B55" s="5">
-        <v>16</v>
-      </c>
-      <c r="C55" s="5">
-        <v>33</v>
-      </c>
-      <c r="E55" s="5">
-        <v>16</v>
-      </c>
-      <c r="F55" s="5">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A56" s="5">
-        <v>47</v>
-      </c>
-      <c r="B56" s="5">
-        <v>14</v>
-      </c>
-      <c r="C56" s="5">
-        <v>32</v>
-      </c>
-      <c r="D56" s="5">
-        <v>3</v>
-      </c>
-      <c r="E56" s="5">
-        <v>14</v>
-      </c>
-      <c r="F56" s="5">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" s="5">
-        <v>46</v>
-      </c>
-      <c r="B57" s="5">
-        <v>12</v>
-      </c>
-      <c r="C57" s="5">
-        <v>31</v>
-      </c>
-      <c r="E57" s="5">
-        <v>12</v>
-      </c>
-      <c r="F57" s="5">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A58" s="5">
-        <v>45</v>
-      </c>
-      <c r="B58" s="5">
-        <v>10</v>
-      </c>
-      <c r="C58" s="5">
-        <v>30</v>
-      </c>
-      <c r="E58" s="5">
-        <v>10</v>
-      </c>
-      <c r="F58" s="5">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A59" s="5">
-        <v>44</v>
-      </c>
-      <c r="B59" s="5">
-        <v>8</v>
-      </c>
-      <c r="C59" s="5">
-        <v>27</v>
-      </c>
-      <c r="D59" s="5">
-        <v>2</v>
-      </c>
-      <c r="E59" s="5">
-        <v>8</v>
-      </c>
-      <c r="F59" s="5">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A60" s="5">
-        <v>43</v>
-      </c>
-      <c r="B60" s="5">
-        <v>6</v>
-      </c>
-      <c r="C60" s="5">
-        <v>26</v>
-      </c>
-      <c r="E60" s="5">
-        <v>6</v>
-      </c>
-      <c r="F60" s="5">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A61" s="5">
-        <v>42</v>
-      </c>
-      <c r="B61" s="5">
-        <v>4</v>
-      </c>
-      <c r="C61" s="5">
-        <v>25</v>
-      </c>
-      <c r="E61" s="5">
-        <v>4</v>
-      </c>
-      <c r="F61" s="5">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62" s="5">
-        <v>41</v>
-      </c>
-      <c r="B62" s="5">
-        <v>2</v>
-      </c>
-      <c r="C62" s="5">
-        <v>24</v>
-      </c>
-      <c r="E62" s="5">
-        <v>2</v>
-      </c>
-      <c r="F62" s="5">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A63" s="5">
-        <v>40</v>
-      </c>
-      <c r="B63" s="5">
-        <v>1</v>
-      </c>
-      <c r="C63" s="5">
-        <v>20</v>
-      </c>
-      <c r="D63" s="5">
-        <v>1</v>
-      </c>
-      <c r="E63" s="5">
-        <v>1</v>
-      </c>
-      <c r="F63" s="5">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A64" s="5">
+      <c r="B64">
         <v>0</v>
       </c>
-      <c r="B64" s="5">
+      <c r="C64">
         <v>0</v>
       </c>
-      <c r="C64" s="5">
+      <c r="D64">
         <v>0</v>
       </c>
-      <c r="D64" s="5">
+      <c r="E64">
         <v>0</v>
       </c>
-      <c r="E64" s="5">
-        <v>0</v>
-      </c>
-      <c r="F64" s="5">
+      <c r="F64">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C14:C17">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E16">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3 G5 G7 G9 C4:C7">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8 C9:C12 H14 H11">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
